--- a/fixtures/demo-workbook/demo-workbook.xlsx
+++ b/fixtures/demo-workbook/demo-workbook.xlsx
@@ -47,7 +47,7 @@
     <t>VERIFIED</t>
   </si>
   <si>
-    <t>GA1CD9F3KXQPLMN7R2WZT8VY</t>
+    <t>GAGCMMI5YDAYYVZDMUOZZXEVS3OSSNKTATYHAFMFCCEISRYZH5F4JZI2</t>
   </si>
   <si>
     <t>ATTESTED</t>
@@ -62,7 +62,7 @@
     <t>Northline Supplies</t>
   </si>
   <si>
-    <t>GB4KP1M9XCLRQZ7N2WYT8VFH</t>
+    <t>GBD3F5E7RO5PRM2X34DKFE5Y4X7C2662BNNIWKQYWV5YKPE7UAPMXG4W</t>
   </si>
   <si>
     <t>2026-01-15</t>
@@ -74,7 +74,7 @@
     <t>Meridian Logistics</t>
   </si>
   <si>
-    <t>GC7QT3N1XMLPRZ9K5WYH8VFJ</t>
+    <t>GBN2IZFPV2SOOKOVRDLVOPUFSUAXPDLC7GJKYBTGUEJW6P6I6CR5IXMX</t>
   </si>
   <si>
     <t>2026-02-01</t>
@@ -86,7 +86,7 @@
     <t>Arclight Components</t>
   </si>
   <si>
-    <t>GAKX9F1D3RTMLPZQ7N2WYH5V</t>
+    <t>GCWHVCDLQWRHPXUJFSSM2J6PEFUHLDBZ77XRWQM5MA3ULYMYY3K7EPNO</t>
   </si>
   <si>
     <t>2026-03-05</t>
@@ -98,7 +98,7 @@
     <t>Harborview Services</t>
   </si>
   <si>
-    <t>GE6YH2T9XMLQRZ4N1WVF7J0E</t>
+    <t>GA2ZWFTZZPRHTU2LRBKFS2VEAVQDBNW7YRISPUQXD3P2UEAANFHAN33C</t>
   </si>
   <si>
     <t>2026-01-20</t>
@@ -185,7 +185,7 @@
     <t>INV-004</t>
   </si>
   <si>
-    <t>GD2RT5W8XKLQPZ1N6MYH9VFJ</t>
+    <t>GBULRZJR3HMP4DRBMT5OFCO6RIX7QYUC5PVHBCZXXLTBLRTYKZQYIVIN</t>
   </si>
   <si>
     <t>sha256:demo-inv-004</t>
